--- a/outs/todo/09_top_results_with_rationale.xlsx
+++ b/outs/todo/09_top_results_with_rationale.xlsx
@@ -18,12 +18,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
   <si>
     <t xml:space="preserve">How to fill this in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rationales were drafted by Claude (AI) from each opportunity's Grants.gov description and the tool's impact scores, then checked against the numbers in each row. Review and edit them before submitting.</t>
   </si>
   <si>
     <t xml:space="preserve">One tab per tier. Each row is an opportunity in that tier in the tool's opening scenario (NC DHHS, plus NC DMVA's two Tier 3 items).</t>
@@ -1741,11 +1738,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -1787,87 +1779,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -1876,7 +1868,7 @@
         <v>71</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" s="8" t="n">
         <v>20</v>
@@ -1885,7 +1877,7 @@
         <v>10584340</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H2" s="8" t="n">
         <v>13</v>
@@ -1900,7 +1892,7 @@
         <v>18.1</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -1909,22 +1901,22 @@
         <v>6.7</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>46434</v>
@@ -1933,19 +1925,19 @@
         <v>7500000</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X2" s="5"/>
       <c r="Y2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="Z2" s="9" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -1954,7 +1946,7 @@
         <v>66</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>10</v>
@@ -1963,7 +1955,7 @@
         <v>10584340</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>13</v>
@@ -1978,7 +1970,7 @@
         <v>19.6</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>1</v>
@@ -1987,22 +1979,22 @@
         <v>6.7</v>
       </c>
       <c r="O3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="T3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U3" s="4" t="n">
         <v>46386</v>
@@ -2011,21 +2003,21 @@
         <v>22024900</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X3" s="5" t="n">
         <v>398400</v>
       </c>
       <c r="Y3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z3" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="Z3" s="9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -2034,7 +2026,7 @@
         <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>10</v>
@@ -2043,7 +2035,7 @@
         <v>10584340</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>13</v>
@@ -2058,7 +2050,7 @@
         <v>19.2</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>1</v>
@@ -2067,22 +2059,22 @@
         <v>6.7</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="R4" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="S4" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>46386</v>
@@ -2091,21 +2083,21 @@
         <v>19182000</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>1215700</v>
       </c>
       <c r="Y4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z4" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="Z4" s="9" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4</v>
@@ -2114,7 +2106,7 @@
         <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>10</v>
@@ -2123,7 +2115,7 @@
         <v>10584340</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>13</v>
@@ -2138,7 +2130,7 @@
         <v>19.5</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>1</v>
@@ -2147,22 +2139,22 @@
         <v>6.7</v>
       </c>
       <c r="O5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="S5" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="T5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U5" s="4" t="n">
         <v>46391</v>
@@ -2171,21 +2163,21 @@
         <v>22000000</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>3500000</v>
       </c>
       <c r="Y5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z5" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="Z5" s="9" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
@@ -2194,7 +2186,7 @@
         <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>10</v>
@@ -2203,7 +2195,7 @@
         <v>10584340</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>13</v>
@@ -2218,7 +2210,7 @@
         <v>19.1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>1</v>
@@ -2227,22 +2219,22 @@
         <v>6.7</v>
       </c>
       <c r="O6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="Q6" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="R6" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>46395</v>
@@ -2251,21 +2243,21 @@
         <v>15335500</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X6" s="5" t="n">
         <v>567000</v>
       </c>
       <c r="Y6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z6" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="Z6" s="9" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>6</v>
@@ -2274,7 +2266,7 @@
         <v>62</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>10</v>
@@ -2283,7 +2275,7 @@
         <v>10584340</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>13</v>
@@ -2298,7 +2290,7 @@
         <v>18.5</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
@@ -2307,22 +2299,22 @@
         <v>6.7</v>
       </c>
       <c r="O7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="S7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>46461</v>
@@ -2331,19 +2323,19 @@
         <v>9000000</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X7" s="5"/>
       <c r="Y7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z7" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="Z7" s="9" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
@@ -2352,7 +2344,7 @@
         <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>10</v>
@@ -2361,7 +2353,7 @@
         <v>10584340</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>13</v>
@@ -2376,7 +2368,7 @@
         <v>18.4</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>1</v>
@@ -2385,22 +2377,22 @@
         <v>6.7</v>
       </c>
       <c r="O8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="R8" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="S8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>46398</v>
@@ -2409,19 +2401,19 @@
         <v>8474576.27118644</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X8" s="5"/>
       <c r="Y8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z8" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="Z8" s="9" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>8</v>
@@ -2430,14 +2422,14 @@
         <v>61</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="7"/>
@@ -2446,7 +2438,7 @@
         <v>33</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>1</v>
@@ -2455,22 +2447,22 @@
         <v>11.1</v>
       </c>
       <c r="O9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="R9" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="S9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="U9" s="4" t="n">
         <v>46531</v>
@@ -2479,19 +2471,19 @@
         <v>41250000</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X9" s="5"/>
       <c r="Y9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z9" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="Z9" s="9" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
@@ -2500,7 +2492,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>10</v>
@@ -2509,7 +2501,7 @@
         <v>1073923</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>1.3</v>
@@ -2524,7 +2516,7 @@
         <v>19.3</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>1</v>
@@ -2533,22 +2525,22 @@
         <v>6.7</v>
       </c>
       <c r="O10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="P10" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="R10" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="S10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>46387</v>
@@ -2557,19 +2549,19 @@
         <v>21716666.6666667</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X10" s="5"/>
       <c r="Y10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z10" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="Z10" s="9" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>10</v>
@@ -2578,7 +2570,7 @@
         <v>56</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>10</v>
@@ -2587,7 +2579,7 @@
         <v>1402172</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>2.7</v>
@@ -2602,7 +2594,7 @@
         <v>18.7</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>1</v>
@@ -2611,22 +2603,22 @@
         <v>6.7</v>
       </c>
       <c r="O11" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="Q11" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="R11" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="R11" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="S11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U11" s="4" t="n">
         <v>46328</v>
@@ -2635,19 +2627,19 @@
         <v>10000000</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X11" s="5"/>
       <c r="Y11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z11" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="Z11" s="9" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>11</v>
@@ -2656,7 +2648,7 @@
         <v>56</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>10</v>
@@ -2665,7 +2657,7 @@
         <v>2322823</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>4.7</v>
@@ -2680,7 +2672,7 @@
         <v>17.6</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>1</v>
@@ -2689,22 +2681,22 @@
         <v>6.7</v>
       </c>
       <c r="O12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="Q12" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="R12" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R12" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="S12" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>46407</v>
@@ -2713,21 +2705,21 @@
         <v>5149000</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X12" s="5" t="n">
         <v>5149000</v>
       </c>
       <c r="Y12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z12" s="9" t="s">
         <v>121</v>
-      </c>
-      <c r="Z12" s="9" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>12</v>
@@ -2736,7 +2728,7 @@
         <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>10</v>
@@ -2745,7 +2737,7 @@
         <v>10584340</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>13</v>
@@ -2760,7 +2752,7 @@
         <v>15.9</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>1</v>
@@ -2769,22 +2761,22 @@
         <v>6.7</v>
       </c>
       <c r="O13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="P13" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="Q13" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="R13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="S13" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="S13" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="T13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>46477</v>
@@ -2793,19 +2785,19 @@
         <v>2750000</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X13" s="5"/>
       <c r="Y13" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z13" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="Z13" s="9" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
@@ -2814,7 +2806,7 @@
         <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>10</v>
@@ -2823,7 +2815,7 @@
         <v>10584340</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>13</v>
@@ -2838,7 +2830,7 @@
         <v>16.2</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>1</v>
@@ -2847,22 +2839,22 @@
         <v>6.7</v>
       </c>
       <c r="O14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="P14" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="Q14" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="R14" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="R14" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="S14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T14" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>46538</v>
@@ -2871,19 +2863,19 @@
         <v>3000000</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X14" s="5"/>
       <c r="Y14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z14" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="Z14" s="9" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>14</v>
@@ -2892,7 +2884,7 @@
         <v>54</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>10</v>
@@ -2901,7 +2893,7 @@
         <v>10584340</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>13</v>
@@ -2916,7 +2908,7 @@
         <v>15.5</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>1</v>
@@ -2925,22 +2917,22 @@
         <v>6.7</v>
       </c>
       <c r="O15" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="P15" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="Q15" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="R15" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="R15" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="S15" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>46503</v>
@@ -2949,19 +2941,19 @@
         <v>2217391.30434783</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X15" s="5"/>
       <c r="Y15" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z15" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="Z15" s="9" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
@@ -2970,7 +2962,7 @@
         <v>50</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>10</v>
@@ -2979,7 +2971,7 @@
         <v>10584340</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H16" s="8" t="n">
         <v>13</v>
@@ -2994,7 +2986,7 @@
         <v>12.7</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1</v>
@@ -3003,22 +2995,22 @@
         <v>6.7</v>
       </c>
       <c r="O16" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="P16" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="R16" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="S16" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="S16" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="T16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>46387</v>
@@ -3027,21 +3019,21 @@
         <v>1140000</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X16" s="5" t="n">
         <v>850000</v>
       </c>
       <c r="Y16" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z16" s="9" t="s">
         <v>148</v>
-      </c>
-      <c r="Z16" s="9" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>16</v>
@@ -3050,7 +3042,7 @@
         <v>49</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>16.7</v>
@@ -3059,7 +3051,7 @@
         <v>10584340</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>21.7</v>
@@ -3068,7 +3060,7 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>1</v>
@@ -3077,39 +3069,39 @@
         <v>11.1</v>
       </c>
       <c r="O17" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="P17" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="P17" s="2" t="s">
+      <c r="Q17" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="Q17" s="2" t="s">
+      <c r="R17" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="R17" s="2" t="s">
+      <c r="S17" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="S17" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="T17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="5"/>
       <c r="W17" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="X17" s="5"/>
       <c r="Y17" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z17" s="9" t="s">
         <v>157</v>
-      </c>
-      <c r="Z17" s="9" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
@@ -3118,7 +3110,7 @@
         <v>48</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>10</v>
@@ -3127,7 +3119,7 @@
         <v>10584340</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>13</v>
@@ -3142,7 +3134,7 @@
         <v>11.9</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>1</v>
@@ -3151,22 +3143,22 @@
         <v>6.7</v>
       </c>
       <c r="O18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="P18" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="P18" s="2" t="s">
+      <c r="Q18" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="Q18" s="2" t="s">
+      <c r="R18" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="R18" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="S18" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>46357</v>
@@ -3175,21 +3167,21 @@
         <v>1000000</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X18" s="5" t="n">
         <v>1000000</v>
       </c>
       <c r="Y18" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z18" s="9" t="s">
         <v>163</v>
-      </c>
-      <c r="Z18" s="9" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>18</v>
@@ -3198,7 +3190,7 @@
         <v>48</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>10</v>
@@ -3207,7 +3199,7 @@
         <v>10584340</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>13</v>
@@ -3222,7 +3214,7 @@
         <v>11.9</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>1</v>
@@ -3231,22 +3223,22 @@
         <v>6.7</v>
       </c>
       <c r="O19" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P19" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="Q19" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="Q19" s="2" t="s">
+      <c r="R19" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="R19" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="S19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T19" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="U19" s="4" t="n">
         <v>46438</v>
@@ -3255,21 +3247,21 @@
         <v>1000000</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X19" s="5" t="n">
         <v>350000</v>
       </c>
       <c r="Y19" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z19" s="9" t="s">
         <v>169</v>
-      </c>
-      <c r="Z19" s="9" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
@@ -3278,7 +3270,7 @@
         <v>47</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>10</v>
@@ -3287,7 +3279,7 @@
         <v>127227</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>0.3</v>
@@ -3302,7 +3294,7 @@
         <v>11.9</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>1</v>
@@ -3311,22 +3303,22 @@
         <v>6.7</v>
       </c>
       <c r="O20" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="P20" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="Q20" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="Q20" s="2" t="s">
+      <c r="R20" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="R20" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="S20" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>46497</v>
@@ -3335,19 +3327,19 @@
         <v>1000000</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X20" s="5"/>
       <c r="Y20" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z20" s="9" t="s">
         <v>176</v>
-      </c>
-      <c r="Z20" s="9" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>20</v>
@@ -3356,7 +3348,7 @@
         <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>10</v>
@@ -3365,7 +3357,7 @@
         <v>10584340</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>13</v>
@@ -3380,7 +3372,7 @@
         <v>10.6</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>1</v>
@@ -3389,22 +3381,22 @@
         <v>6.7</v>
       </c>
       <c r="O21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P21" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="Q21" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="Q21" s="2" t="s">
+      <c r="R21" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="R21" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="S21" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>46464</v>
@@ -3413,19 +3405,19 @@
         <v>750000</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X21" s="5"/>
       <c r="Y21" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z21" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="Z21" s="9" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
@@ -3434,7 +3426,7 @@
         <v>44</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>10</v>
@@ -3443,7 +3435,7 @@
         <v>10584340</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>13</v>
@@ -3458,7 +3450,7 @@
         <v>9.6</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>1</v>
@@ -3467,22 +3459,22 @@
         <v>6.7</v>
       </c>
       <c r="O22" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="P22" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="Q22" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="R22" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="S22" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U22" s="4" t="n">
         <v>46405</v>
@@ -3491,19 +3483,19 @@
         <v>700000</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X22" s="5"/>
       <c r="Y22" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z22" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="Z22" s="9" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>22</v>
@@ -3512,7 +3504,7 @@
         <v>44</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>10</v>
@@ -3521,7 +3513,7 @@
         <v>10584340</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>13</v>
@@ -3536,7 +3528,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>1</v>
@@ -3545,22 +3537,22 @@
         <v>6.7</v>
       </c>
       <c r="O23" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="P23" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="Q23" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="Q23" s="2" t="s">
+      <c r="R23" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="R23" s="2" t="s">
-        <v>193</v>
-      </c>
       <c r="S23" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U23" s="4" t="n">
         <v>46468</v>
@@ -3569,21 +3561,21 @@
         <v>725000</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X23" s="5" t="n">
         <v>500000</v>
       </c>
       <c r="Y23" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z23" s="9" t="s">
         <v>194</v>
-      </c>
-      <c r="Z23" s="9" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
@@ -3592,7 +3584,7 @@
         <v>43</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>10</v>
@@ -3601,7 +3593,7 @@
         <v>10584340</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>13</v>
@@ -3616,7 +3608,7 @@
         <v>9.4</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>1</v>
@@ -3625,22 +3617,22 @@
         <v>6.7</v>
       </c>
       <c r="O24" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="P24" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="Q24" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="Q24" s="2" t="s">
+      <c r="R24" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="R24" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="S24" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U24" s="4" t="n">
         <v>46386</v>
@@ -3649,21 +3641,21 @@
         <v>685000</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X24" s="5" t="n">
         <v>150000</v>
       </c>
       <c r="Y24" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z24" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="Z24" s="9" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>24</v>
@@ -3672,7 +3664,7 @@
         <v>42</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>10</v>
@@ -3681,7 +3673,7 @@
         <v>10584340</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>13</v>
@@ -3696,7 +3688,7 @@
         <v>9.2</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>1</v>
@@ -3705,22 +3697,22 @@
         <v>6.7</v>
       </c>
       <c r="O25" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="P25" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="P25" s="2" t="s">
+      <c r="Q25" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="Q25" s="2" t="s">
+      <c r="R25" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="R25" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="S25" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U25" s="4" t="n">
         <v>46466</v>
@@ -3729,19 +3721,19 @@
         <v>650000</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X25" s="5"/>
       <c r="Y25" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="Z25" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="Z25" s="9" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>25</v>
@@ -3750,7 +3742,7 @@
         <v>39</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>10</v>
@@ -3759,7 +3751,7 @@
         <v>10584340</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>13</v>
@@ -3774,7 +3766,7 @@
         <v>6.9</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>1</v>
@@ -3783,22 +3775,22 @@
         <v>6.7</v>
       </c>
       <c r="O26" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="P26" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="P26" s="2" t="s">
+      <c r="Q26" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="Q26" s="2" t="s">
+      <c r="R26" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="R26" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="S26" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U26" s="4" t="n">
         <v>46462</v>
@@ -3807,21 +3799,21 @@
         <v>500000</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X26" s="5" t="n">
         <v>300000</v>
       </c>
       <c r="Y26" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z26" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="Z26" s="9" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>26</v>
@@ -3830,7 +3822,7 @@
         <v>39</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>10</v>
@@ -3839,7 +3831,7 @@
         <v>10584340</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>13</v>
@@ -3854,7 +3846,7 @@
         <v>6.9</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>1</v>
@@ -3863,22 +3855,22 @@
         <v>6.7</v>
       </c>
       <c r="O27" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="P27" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="P27" s="2" t="s">
+      <c r="Q27" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="Q27" s="2" t="s">
+      <c r="R27" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="R27" s="2" t="s">
-        <v>217</v>
-      </c>
       <c r="S27" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U27" s="4" t="n">
         <v>46532</v>
@@ -3887,21 +3879,21 @@
         <v>500000</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X27" s="5" t="n">
         <v>250000</v>
       </c>
       <c r="Y27" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z27" s="9" t="s">
         <v>218</v>
-      </c>
-      <c r="Z27" s="9" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>27</v>
@@ -3910,7 +3902,7 @@
         <v>35</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>10</v>
@@ -3919,7 +3911,7 @@
         <v>10584340</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>13</v>
@@ -3934,7 +3926,7 @@
         <v>3.9</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>1</v>
@@ -3943,22 +3935,22 @@
         <v>6.7</v>
       </c>
       <c r="O28" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="P28" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="P28" s="2" t="s">
+      <c r="Q28" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="Q28" s="2" t="s">
+      <c r="R28" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="R28" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="S28" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U28" s="4" t="n">
         <v>46508</v>
@@ -3967,14 +3959,14 @@
         <v>300000</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X28" s="5"/>
       <c r="Y28" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="Z28" s="9" t="s">
         <v>224</v>
-      </c>
-      <c r="Z28" s="9" t="s">
-        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -4048,87 +4040,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -4137,7 +4129,7 @@
         <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" s="12" t="n">
         <v>20</v>
@@ -4146,7 +4138,7 @@
         <v>10584340</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H2" s="12" t="n">
         <v>13</v>
@@ -4161,7 +4153,7 @@
         <v>17.3</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -4170,22 +4162,22 @@
         <v>6.7</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>46429</v>
@@ -4194,21 +4186,21 @@
         <v>5000000</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X2" s="5" t="n">
         <v>50000</v>
       </c>
       <c r="Y2" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z2" s="9" t="s">
         <v>232</v>
-      </c>
-      <c r="Z2" s="9" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -4217,7 +4209,7 @@
         <v>61</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>20</v>
@@ -4226,7 +4218,7 @@
         <v>127227</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H3" s="12" t="n">
         <v>0.3</v>
@@ -4241,7 +4233,7 @@
         <v>15.3</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>1</v>
@@ -4250,22 +4242,22 @@
         <v>6.7</v>
       </c>
       <c r="O3" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>238</v>
-      </c>
       <c r="T3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U3" s="4" t="n">
         <v>46510</v>
@@ -4274,19 +4266,19 @@
         <v>2141025.64102564</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X3" s="5"/>
       <c r="Y3" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z3" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="Z3" s="9" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -4295,7 +4287,7 @@
         <v>61</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>10</v>
@@ -4304,7 +4296,7 @@
         <v>2322823</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H4" s="12" t="n">
         <v>4.7</v>
@@ -4319,7 +4311,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>1</v>
@@ -4328,22 +4320,22 @@
         <v>6.7</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="S4" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="T4" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>46661</v>
@@ -4352,21 +4344,21 @@
         <v>100000000</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>1000000</v>
       </c>
       <c r="Y4" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z4" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="Z4" s="9" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4</v>
@@ -4375,7 +4367,7 @@
         <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>10</v>
@@ -4384,7 +4376,7 @@
         <v>10584340</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H5" s="12" t="n">
         <v>13</v>
@@ -4399,7 +4391,7 @@
         <v>17.8</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>1</v>
@@ -4408,22 +4400,22 @@
         <v>6.7</v>
       </c>
       <c r="O5" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="R5" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="S5" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U5" s="4" t="n">
         <v>46331</v>
@@ -4432,21 +4424,21 @@
         <v>6000000</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>1750000</v>
       </c>
       <c r="Y5" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="Z5" s="9" t="s">
         <v>252</v>
-      </c>
-      <c r="Z5" s="9" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
@@ -4455,7 +4447,7 @@
         <v>60</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>10</v>
@@ -4464,7 +4456,7 @@
         <v>10584340</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>13</v>
@@ -4479,7 +4471,7 @@
         <v>17.7</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>1</v>
@@ -4488,22 +4480,22 @@
         <v>6.7</v>
       </c>
       <c r="O6" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="R6" s="2" t="s">
-        <v>257</v>
-      </c>
       <c r="S6" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>46357</v>
@@ -4512,21 +4504,21 @@
         <v>5750000</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X6" s="5" t="n">
         <v>3000000</v>
       </c>
       <c r="Y6" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z6" s="9" t="s">
         <v>258</v>
-      </c>
-      <c r="Z6" s="9" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>6</v>
@@ -4535,7 +4527,7 @@
         <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>20</v>
@@ -4544,7 +4536,7 @@
         <v>10584340</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>13</v>
@@ -4559,7 +4551,7 @@
         <v>12.4</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
@@ -4568,22 +4560,22 @@
         <v>6.7</v>
       </c>
       <c r="O7" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="S7" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>46507</v>
@@ -4592,19 +4584,19 @@
         <v>1002916.66666667</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X7" s="5"/>
       <c r="Y7" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="Z7" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="Z7" s="9" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
@@ -4613,7 +4605,7 @@
         <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>10</v>
@@ -4622,7 +4614,7 @@
         <v>10584340</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>13</v>
@@ -4637,7 +4629,7 @@
         <v>17.1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>1</v>
@@ -4646,22 +4638,22 @@
         <v>6.7</v>
       </c>
       <c r="O8" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="R8" s="2" t="s">
-        <v>269</v>
-      </c>
       <c r="S8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>46412</v>
@@ -4670,21 +4662,21 @@
         <v>4900000</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>790000</v>
       </c>
       <c r="Y8" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="Z8" s="9" t="s">
         <v>270</v>
-      </c>
-      <c r="Z8" s="9" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>8</v>
@@ -4693,7 +4685,7 @@
         <v>58</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>10</v>
@@ -4702,7 +4694,7 @@
         <v>10584340</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>13</v>
@@ -4717,7 +4709,7 @@
         <v>16.8</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>1</v>
@@ -4726,22 +4718,22 @@
         <v>6.7</v>
       </c>
       <c r="O9" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="R9" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="S9" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U9" s="4" t="n">
         <v>46469</v>
@@ -4750,19 +4742,19 @@
         <v>3625000</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X9" s="5"/>
       <c r="Y9" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z9" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="Z9" s="9" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
@@ -4771,14 +4763,14 @@
         <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="11"/>
@@ -4787,7 +4779,7 @@
         <v>28.9</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>1</v>
@@ -4796,22 +4788,22 @@
         <v>11.1</v>
       </c>
       <c r="O10" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="P10" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="R10" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="S10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>46469</v>
@@ -4820,21 +4812,21 @@
         <v>5000000</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X10" s="5" t="n">
         <v>5000000</v>
       </c>
       <c r="Y10" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="Z10" s="9" t="s">
         <v>282</v>
-      </c>
-      <c r="Z10" s="9" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>10</v>
@@ -4843,7 +4835,7 @@
         <v>57</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>10</v>
@@ -4852,7 +4844,7 @@
         <v>2322823</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>4.7</v>
@@ -4867,7 +4859,7 @@
         <v>18</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>1</v>
@@ -4876,22 +4868,22 @@
         <v>6.7</v>
       </c>
       <c r="O11" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="Q11" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="R11" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="R11" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="S11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U11" s="4" t="n">
         <v>46498</v>
@@ -4900,21 +4892,21 @@
         <v>6750000</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X11" s="5" t="n">
         <v>6750000</v>
       </c>
       <c r="Y11" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z11" s="9" t="s">
         <v>288</v>
-      </c>
-      <c r="Z11" s="9" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>11</v>
@@ -4923,7 +4915,7 @@
         <v>56</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>10</v>
@@ -4932,7 +4924,7 @@
         <v>2322823</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>4.7</v>
@@ -4947,7 +4939,7 @@
         <v>17.3</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>1</v>
@@ -4956,22 +4948,22 @@
         <v>6.7</v>
       </c>
       <c r="O12" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="Q12" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="R12" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="R12" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="S12" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>46441</v>
@@ -4980,21 +4972,21 @@
         <v>5000000</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X12" s="5" t="n">
         <v>5000000</v>
       </c>
       <c r="Y12" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="Z12" s="9" t="s">
         <v>294</v>
-      </c>
-      <c r="Z12" s="9" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>12</v>
@@ -5003,14 +4995,14 @@
         <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>33.3</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="11"/>
@@ -5019,7 +5011,7 @@
         <v>11.6</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>1</v>
@@ -5028,22 +5020,22 @@
         <v>11.1</v>
       </c>
       <c r="O13" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="P13" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="Q13" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="R13" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="R13" s="2" t="s">
-        <v>299</v>
-      </c>
       <c r="S13" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>46483</v>
@@ -5052,19 +5044,19 @@
         <v>500000</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X13" s="5"/>
       <c r="Y13" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z13" s="9" t="s">
         <v>300</v>
-      </c>
-      <c r="Z13" s="9" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
@@ -5073,7 +5065,7 @@
         <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>20</v>
@@ -5082,7 +5074,7 @@
         <v>1402172</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>2.7</v>
@@ -5097,7 +5089,7 @@
         <v>13</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>1</v>
@@ -5106,22 +5098,22 @@
         <v>6.7</v>
       </c>
       <c r="O14" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="P14" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="Q14" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="R14" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="S14" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="S14" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="T14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>46494</v>
@@ -5130,21 +5122,21 @@
         <v>1200000</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X14" s="5" t="n">
         <v>650000</v>
       </c>
       <c r="Y14" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="Z14" s="9" t="s">
         <v>307</v>
-      </c>
-      <c r="Z14" s="9" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>14</v>
@@ -5153,7 +5145,7 @@
         <v>56</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>10</v>
@@ -5162,7 +5154,7 @@
         <v>10584340</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>13</v>
@@ -5177,7 +5169,7 @@
         <v>15.9</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>1</v>
@@ -5186,22 +5178,22 @@
         <v>6.7</v>
       </c>
       <c r="O15" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="P15" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="Q15" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="R15" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="R15" s="2" t="s">
-        <v>312</v>
-      </c>
       <c r="S15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T15" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>46539</v>
@@ -5210,19 +5202,19 @@
         <v>2750000</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X15" s="5"/>
       <c r="Y15" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="Z15" s="9" t="s">
         <v>313</v>
-      </c>
-      <c r="Z15" s="9" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
@@ -5231,7 +5223,7 @@
         <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>20</v>
@@ -5240,7 +5232,7 @@
         <v>2322823</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>4.7</v>
@@ -5255,7 +5247,7 @@
         <v>9.6</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1</v>
@@ -5264,22 +5256,22 @@
         <v>6.7</v>
       </c>
       <c r="O16" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="P16" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="R16" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="R16" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="S16" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>46498</v>
@@ -5288,21 +5280,21 @@
         <v>700000</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X16" s="5" t="n">
         <v>700000</v>
       </c>
       <c r="Y16" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z16" s="9" t="s">
         <v>319</v>
-      </c>
-      <c r="Z16" s="9" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>16</v>
@@ -5311,7 +5303,7 @@
         <v>51</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>10</v>
@@ -5320,7 +5312,7 @@
         <v>10584340</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>13</v>
@@ -5335,7 +5327,7 @@
         <v>13.4</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>1</v>
@@ -5344,22 +5336,22 @@
         <v>6.7</v>
       </c>
       <c r="O17" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="P17" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="P17" s="2" t="s">
+      <c r="Q17" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="Q17" s="2" t="s">
+      <c r="R17" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="R17" s="2" t="s">
-        <v>324</v>
-      </c>
       <c r="S17" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U17" s="4" t="n">
         <v>46444</v>
@@ -5368,21 +5360,21 @@
         <v>1400000</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X17" s="5" t="n">
         <v>500000</v>
       </c>
       <c r="Y17" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="Z17" s="9" t="s">
         <v>325</v>
-      </c>
-      <c r="Z17" s="9" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
@@ -5391,7 +5383,7 @@
         <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>10</v>
@@ -5400,7 +5392,7 @@
         <v>10584340</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>13</v>
@@ -5415,7 +5407,7 @@
         <v>13.5</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>1</v>
@@ -5424,22 +5416,22 @@
         <v>6.7</v>
       </c>
       <c r="O18" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="P18" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="P18" s="2" t="s">
+      <c r="Q18" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="Q18" s="2" t="s">
+      <c r="R18" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="R18" s="2" t="s">
-        <v>330</v>
-      </c>
       <c r="S18" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>46454</v>
@@ -5448,19 +5440,19 @@
         <v>1423076.92307692</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X18" s="5"/>
       <c r="Y18" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="Z18" s="9" t="s">
         <v>331</v>
-      </c>
-      <c r="Z18" s="9" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>18</v>
@@ -5469,7 +5461,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>10</v>
@@ -5478,7 +5470,7 @@
         <v>1402172</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>2.7</v>
@@ -5493,7 +5485,7 @@
         <v>15.7</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>1</v>
@@ -5502,22 +5494,22 @@
         <v>6.7</v>
       </c>
       <c r="O19" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="P19" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="Q19" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="Q19" s="2" t="s">
+      <c r="R19" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="R19" s="2" t="s">
-        <v>336</v>
-      </c>
       <c r="S19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T19" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="U19" s="4" t="n">
         <v>46461</v>
@@ -5526,19 +5518,19 @@
         <v>2500000</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X19" s="5"/>
       <c r="Y19" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="Z19" s="9" t="s">
         <v>337</v>
-      </c>
-      <c r="Z19" s="9" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
@@ -5547,7 +5539,7 @@
         <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>16.7</v>
@@ -5556,7 +5548,7 @@
         <v>10584340</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>21.7</v>
@@ -5565,7 +5557,7 @@
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
       <c r="L20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>1</v>
@@ -5574,41 +5566,41 @@
         <v>11.1</v>
       </c>
       <c r="O20" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="P20" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="Q20" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="Q20" s="2" t="s">
+      <c r="R20" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="R20" s="2" t="s">
+      <c r="S20" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="S20" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="T20" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>46783</v>
       </c>
       <c r="V20" s="5"/>
       <c r="W20" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="X20" s="5"/>
       <c r="Y20" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="Z20" s="9" t="s">
         <v>344</v>
-      </c>
-      <c r="Z20" s="9" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>20</v>
@@ -5617,7 +5609,7 @@
         <v>48</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>10</v>
@@ -5626,7 +5618,7 @@
         <v>10584340</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>13</v>
@@ -5641,7 +5633,7 @@
         <v>11.9</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>1</v>
@@ -5650,22 +5642,22 @@
         <v>6.7</v>
       </c>
       <c r="O21" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="P21" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="Q21" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="Q21" s="2" t="s">
+      <c r="R21" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="R21" s="2" t="s">
-        <v>349</v>
-      </c>
       <c r="S21" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>46331</v>
@@ -5674,21 +5666,21 @@
         <v>1000000</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X21" s="5" t="n">
         <v>750000</v>
       </c>
       <c r="Y21" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="Z21" s="9" t="s">
         <v>350</v>
-      </c>
-      <c r="Z21" s="9" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
@@ -5697,7 +5689,7 @@
         <v>46</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>10</v>
@@ -5706,7 +5698,7 @@
         <v>10584340</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>13</v>
@@ -5721,7 +5713,7 @@
         <v>11.3</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>1</v>
@@ -5730,22 +5722,22 @@
         <v>6.7</v>
       </c>
       <c r="O22" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="P22" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="Q22" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="R22" s="2" t="s">
-        <v>355</v>
-      </c>
       <c r="S22" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U22" s="4" t="n">
         <v>46455</v>
@@ -5754,21 +5746,21 @@
         <v>900000</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X22" s="5" t="n">
         <v>450000</v>
       </c>
       <c r="Y22" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="Z22" s="9" t="s">
         <v>356</v>
-      </c>
-      <c r="Z22" s="9" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>22</v>
@@ -5777,7 +5769,7 @@
         <v>41</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>10</v>
@@ -5786,7 +5778,7 @@
         <v>10584340</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>13</v>
@@ -5801,7 +5793,7 @@
         <v>8.4</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>1</v>
@@ -5810,22 +5802,22 @@
         <v>6.7</v>
       </c>
       <c r="O23" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="P23" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="Q23" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="Q23" s="2" t="s">
+      <c r="R23" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="R23" s="2" t="s">
-        <v>361</v>
-      </c>
       <c r="S23" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U23" s="4" t="n">
         <v>47052</v>
@@ -5834,21 +5826,21 @@
         <v>550000</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X23" s="5" t="n">
         <v>50000</v>
       </c>
       <c r="Y23" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="Z23" s="9" t="s">
         <v>362</v>
-      </c>
-      <c r="Z23" s="9" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
@@ -5857,7 +5849,7 @@
         <v>37</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>10</v>
@@ -5866,7 +5858,7 @@
         <v>10584340</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>13</v>
@@ -5881,7 +5873,7 @@
         <v>5.3</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>1</v>
@@ -5890,22 +5882,22 @@
         <v>6.7</v>
       </c>
       <c r="O24" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="P24" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="Q24" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="Q24" s="2" t="s">
+      <c r="R24" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="R24" s="2" t="s">
-        <v>367</v>
-      </c>
       <c r="S24" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U24" s="4" t="n">
         <v>46510</v>
@@ -5914,21 +5906,21 @@
         <v>450000</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X24" s="5" t="n">
         <v>450000</v>
       </c>
       <c r="Y24" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="Z24" s="9" t="s">
         <v>368</v>
-      </c>
-      <c r="Z24" s="9" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>24</v>
@@ -5937,7 +5929,7 @@
         <v>29</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>16.7</v>
@@ -5946,7 +5938,7 @@
         <v>618846</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>1.7</v>
@@ -5955,7 +5947,7 @@
       <c r="J25" s="12"/>
       <c r="K25" s="12"/>
       <c r="L25" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>1</v>
@@ -5964,34 +5956,34 @@
         <v>11.1</v>
       </c>
       <c r="O25" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="P25" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="P25" s="2" t="s">
+      <c r="Q25" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="Q25" s="2" t="s">
+      <c r="R25" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="R25" s="2" t="s">
+      <c r="S25" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="S25" s="2" t="s">
-        <v>375</v>
-      </c>
       <c r="T25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="5"/>
       <c r="W25" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="X25" s="5"/>
       <c r="Y25" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="Z25" s="9" t="s">
         <v>376</v>
-      </c>
-      <c r="Z25" s="9" t="s">
-        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -6062,87 +6054,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -6151,7 +6143,7 @@
         <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" s="15" t="n">
         <v>20</v>
@@ -6160,7 +6152,7 @@
         <v>10584340</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H2" s="15" t="n">
         <v>13</v>
@@ -6175,7 +6167,7 @@
         <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -6184,22 +6176,22 @@
         <v>6.7</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>382</v>
-      </c>
       <c r="T2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>46346</v>
@@ -6208,21 +6200,21 @@
         <v>15000000</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X2" s="5" t="n">
         <v>500000</v>
       </c>
       <c r="Y2" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="Z2" s="9" t="s">
         <v>383</v>
-      </c>
-      <c r="Z2" s="9" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -6231,7 +6223,7 @@
         <v>67</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="15" t="n">
         <v>20</v>
@@ -6240,7 +6232,7 @@
         <v>127227</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H3" s="15" t="n">
         <v>0.3</v>
@@ -6255,7 +6247,7 @@
         <v>19.9</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>1</v>
@@ -6264,22 +6256,22 @@
         <v>6.7</v>
       </c>
       <c r="O3" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="R3" s="2" t="s">
-        <v>388</v>
-      </c>
       <c r="S3" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U3" s="4" t="n">
         <v>46464</v>
@@ -6288,21 +6280,21 @@
         <v>48596938</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X3" s="5" t="n">
         <v>3285203</v>
       </c>
       <c r="Y3" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="Z3" s="9" t="s">
         <v>389</v>
-      </c>
-      <c r="Z3" s="9" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -6311,7 +6303,7 @@
         <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" s="15" t="n">
         <v>10</v>
@@ -6320,7 +6312,7 @@
         <v>10584340</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H4" s="15" t="n">
         <v>13</v>
@@ -6335,7 +6327,7 @@
         <v>19.5</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>1</v>
@@ -6344,22 +6336,22 @@
         <v>6.7</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="S4" s="2" t="s">
-        <v>395</v>
-      </c>
       <c r="T4" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>46398</v>
@@ -6368,21 +6360,21 @@
         <v>22000000</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>200000</v>
       </c>
       <c r="Y4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="Z4" s="9" t="s">
         <v>396</v>
-      </c>
-      <c r="Z4" s="9" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -6391,7 +6383,7 @@
         <v>77</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" s="15" t="n">
         <v>20</v>
@@ -6400,7 +6392,7 @@
         <v>618846</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>10</v>
@@ -6415,7 +6407,7 @@
         <v>20</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>1</v>
@@ -6424,43 +6416,43 @@
         <v>6.7</v>
       </c>
       <c r="O5" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="S5" s="2" t="s">
-        <v>404</v>
-      </c>
       <c r="T5" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="5" t="n">
         <v>275000000</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>260000</v>
       </c>
       <c r="Y5" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="Z5" s="9" t="s">
         <v>405</v>
-      </c>
-      <c r="Z5" s="9" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
@@ -6469,7 +6461,7 @@
         <v>61</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" s="15" t="n">
         <v>33.3</v>
@@ -6478,7 +6470,7 @@
         <v>618846</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>16.7</v>
@@ -6487,7 +6479,7 @@
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
       <c r="L6" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>1</v>
@@ -6496,39 +6488,39 @@
         <v>11.1</v>
       </c>
       <c r="O6" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>375</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="5"/>
       <c r="W6" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="X6" s="5"/>
       <c r="Y6" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Z6" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>3</v>
@@ -6537,7 +6529,7 @@
         <v>37</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="15" t="n">
         <v>20</v>
@@ -6546,7 +6538,7 @@
         <v>618846</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>10</v>
@@ -6561,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
@@ -6570,22 +6562,22 @@
         <v>6.7</v>
       </c>
       <c r="O7" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>412</v>
-      </c>
       <c r="T7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>46486</v>
@@ -6594,16 +6586,16 @@
         <v>400000</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>50000</v>
       </c>
       <c r="Y7" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="Z7" s="9" t="s">
         <v>413</v>
-      </c>
-      <c r="Z7" s="9" t="s">
-        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/outs/todo/09_top_results_with_rationale.xlsx
+++ b/outs/todo/09_top_results_with_rationale.xlsx
@@ -6,7 +6,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="How to fill this in" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EXPLANATION" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Tier 1 - Writer can act" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Tier 2 - Supervisor" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Tier 3 - Secretary or legis." sheetId="4" state="visible" r:id="rId4"/>
@@ -18,45 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
-  <si>
-    <t xml:space="preserve">How to fill this in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One tab per tier. Each row is an opportunity in that tier in the tool's opening scenario (NC DHHS, plus NC DMVA's two Tier 3 items).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each rationale says why the opportunity ranks where it does and what the grant funds. Our five criteria:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deadline and award come from each opportunity's current record on Grants.gov (checked Sept 29-30, 2026). Forecast deadlines are Grants.gov's estimates. The award is Grants.gov's stated award ceiling; where it states none, the award is estimated as total program funding divided by the expected number of awards, and the Award source column says so. A blank award means Grants.gov gives neither.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impact score (0-100) orders opportunities within a tier only; it never moves anything between tiers. For each of five parts the sheet shows the actual number and the points it adds; the points add up to the score (small differences are rounding).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Plan fit: the AI labeler's rating of fit with the agency's strategic plan. Strong earns full points, partial half, none zero.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  People reached: how many North Carolinians are in the population the opportunity serves (the population is named in the next column).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Help per person: the award per recipient divided by that population.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Award size: the award per recipient (shown in the Award per recipient column, with its source).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Program priorities: the writer's weight for the opportunity's program area, out of 3. The default is 1 for every area.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">People reached, help per person and award size earn points by how their number ranks against all the opportunities in the tool's view (about 400), not by the number alone. The biggest number gets full points; the median gets about half.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">With the default equal weights, each part can add at most 100 / (number of parts with a number): 20 points when all five have one. A blank part has no number, and the others share its points. People reached is blank when the population served has no NC count (people with a substance use disorder); help per person is blank when either the award or the people count is.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grants.gov ID is the number in grants.gov listing addresses; Simpler.Grants.gov ID is the code in the link, which opens the listing.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="403">
+  <si>
+    <t xml:space="preserve">Our tool sorted grant opportunities into three tiers, instead of a singular list. These tiers are differentiated by the level of authority needed from a grant coordinator's perspective. Tier 1 grants can be directly acted upon by the grant writer using the tool. Tier 2 opportunities would need approval by a supervisor. Tier 3 grants, due to high matching costs or other factors, need oversight from upper legislature. The 3 tiers allow a user to make desicions about opportunities based on their capabilities and their priorities. Furthermore, within the tiers, the grants are sorted based on an "impact score" which is calculated with multiple metrics, including plan fit with the agency, people reached, population reached, help per person, and award size. While the weights for these metrics were equal, a user of our tool can adjust these weights according to their priorities. Also, there are a few opportunities chosen for the DMVA on this list, to showcase the generalizability of our model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How these results were ranked:</t>
   </si>
   <si>
     <t xml:space="preserve">Agency</t>
@@ -1166,7 +1133,7 @@
     <t xml:space="preserve">HHS-ACF</t>
   </si>
   <si>
-    <t xml:space="preserve">Top ranked in Tier 3 for strong plan fit and a large award (up to $15M), funding statewide early care and education data and technology infrastructure, but its 30% match and required state designation need the secretary.</t>
+    <t xml:space="preserve">Top ranked in Tier 3 for strong plan fit and a large award (up to $15M), funding statewide early care, education data and technology infrastructure, but its 30% match and required state designation need the secretary.</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/8d272419-96d1-4898-9706-0d86a1e63c03</t>
@@ -1205,7 +1172,7 @@
     <t xml:space="preserve">HHS-OPHS</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranked for a large award (up to $22M) and help per person, funding Title X family planning services statewide, with a required match that the data file missed and that likely needs an appropriation.</t>
+    <t xml:space="preserve">Ranked for a large award (up to $22M), help per person, and funding Title X family planning services statewide, with a required match that the data file missed and that likely needs an appropriation.</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/770eae58-b245-4431-a4b8-7b1aca9e917f</t>
@@ -1232,7 +1199,7 @@
     <t xml:space="preserve">VA-CSHF</t>
   </si>
   <si>
-    <t xml:space="preserve">Top ranked for DMVA for strong plan fit and the highest help per veteran (about $444), funding construction and modernization of State Veterans Homes, which needs a 35% state match and an appropriation.</t>
+    <t xml:space="preserve">Top ranked for DMVA strong plan fit, the highest help per veteran (about $444), and funding construction and modernization of State Veterans Homes, but needs a 35% state match and an appropriation.</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/59462b36-6d05-4832-a628-427f72260f3d</t>
@@ -1675,67 +1642,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1779,87 +1691,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -1868,7 +1780,7 @@
         <v>71</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E2" s="8" t="n">
         <v>20</v>
@@ -1877,7 +1789,7 @@
         <v>10584340</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H2" s="8" t="n">
         <v>13</v>
@@ -1892,7 +1804,7 @@
         <v>18.1</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -1901,22 +1813,22 @@
         <v>6.7</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>46434</v>
@@ -1925,19 +1837,19 @@
         <v>7500000</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X2" s="5"/>
       <c r="Y2" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="Z2" s="9" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -1946,7 +1858,7 @@
         <v>66</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>10</v>
@@ -1955,7 +1867,7 @@
         <v>10584340</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>13</v>
@@ -1970,7 +1882,7 @@
         <v>19.6</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>1</v>
@@ -1979,22 +1891,22 @@
         <v>6.7</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U3" s="4" t="n">
         <v>46386</v>
@@ -2003,21 +1915,21 @@
         <v>22024900</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X3" s="5" t="n">
         <v>398400</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -2026,7 +1938,7 @@
         <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>10</v>
@@ -2035,7 +1947,7 @@
         <v>10584340</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>13</v>
@@ -2050,7 +1962,7 @@
         <v>19.2</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>1</v>
@@ -2059,22 +1971,22 @@
         <v>6.7</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>46386</v>
@@ -2083,21 +1995,21 @@
         <v>19182000</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>1215700</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4</v>
@@ -2106,7 +2018,7 @@
         <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>10</v>
@@ -2115,7 +2027,7 @@
         <v>10584340</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>13</v>
@@ -2130,7 +2042,7 @@
         <v>19.5</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>1</v>
@@ -2139,22 +2051,22 @@
         <v>6.7</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U5" s="4" t="n">
         <v>46391</v>
@@ -2163,21 +2075,21 @@
         <v>22000000</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>3500000</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
@@ -2186,7 +2098,7 @@
         <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>10</v>
@@ -2195,7 +2107,7 @@
         <v>10584340</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>13</v>
@@ -2210,7 +2122,7 @@
         <v>19.1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>1</v>
@@ -2219,22 +2131,22 @@
         <v>6.7</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>46395</v>
@@ -2243,21 +2155,21 @@
         <v>15335500</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X6" s="5" t="n">
         <v>567000</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="Z6" s="9" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>6</v>
@@ -2266,7 +2178,7 @@
         <v>62</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>10</v>
@@ -2275,7 +2187,7 @@
         <v>10584340</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>13</v>
@@ -2290,7 +2202,7 @@
         <v>18.5</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
@@ -2299,22 +2211,22 @@
         <v>6.7</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>46461</v>
@@ -2323,19 +2235,19 @@
         <v>9000000</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X7" s="5"/>
       <c r="Y7" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="Z7" s="9" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
@@ -2344,7 +2256,7 @@
         <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>10</v>
@@ -2353,7 +2265,7 @@
         <v>10584340</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>13</v>
@@ -2368,7 +2280,7 @@
         <v>18.4</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>1</v>
@@ -2377,22 +2289,22 @@
         <v>6.7</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>46398</v>
@@ -2401,19 +2313,19 @@
         <v>8474576.27118644</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X8" s="5"/>
       <c r="Y8" s="2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="Z8" s="9" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>8</v>
@@ -2422,14 +2334,14 @@
         <v>61</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="7"/>
@@ -2438,7 +2350,7 @@
         <v>33</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>1</v>
@@ -2447,22 +2359,22 @@
         <v>11.1</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U9" s="4" t="n">
         <v>46531</v>
@@ -2471,19 +2383,19 @@
         <v>41250000</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X9" s="5"/>
       <c r="Y9" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="Z9" s="9" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
@@ -2492,7 +2404,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>10</v>
@@ -2501,7 +2413,7 @@
         <v>1073923</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>1.3</v>
@@ -2516,7 +2428,7 @@
         <v>19.3</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>1</v>
@@ -2525,22 +2437,22 @@
         <v>6.7</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>46387</v>
@@ -2549,19 +2461,19 @@
         <v>21716666.6666667</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X10" s="5"/>
       <c r="Y10" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="Z10" s="9" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>10</v>
@@ -2570,7 +2482,7 @@
         <v>56</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>10</v>
@@ -2579,7 +2491,7 @@
         <v>1402172</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>2.7</v>
@@ -2594,7 +2506,7 @@
         <v>18.7</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>1</v>
@@ -2603,22 +2515,22 @@
         <v>6.7</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U11" s="4" t="n">
         <v>46328</v>
@@ -2627,19 +2539,19 @@
         <v>10000000</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X11" s="5"/>
       <c r="Y11" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="Z11" s="9" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>11</v>
@@ -2648,7 +2560,7 @@
         <v>56</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>10</v>
@@ -2657,7 +2569,7 @@
         <v>2322823</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>4.7</v>
@@ -2672,7 +2584,7 @@
         <v>17.6</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>1</v>
@@ -2681,22 +2593,22 @@
         <v>6.7</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>46407</v>
@@ -2705,21 +2617,21 @@
         <v>5149000</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X12" s="5" t="n">
         <v>5149000</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="Z12" s="9" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>12</v>
@@ -2728,7 +2640,7 @@
         <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>10</v>
@@ -2737,7 +2649,7 @@
         <v>10584340</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>13</v>
@@ -2752,7 +2664,7 @@
         <v>15.9</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>1</v>
@@ -2761,22 +2673,22 @@
         <v>6.7</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>46477</v>
@@ -2785,19 +2697,19 @@
         <v>2750000</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X13" s="5"/>
       <c r="Y13" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="Z13" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
@@ -2806,7 +2718,7 @@
         <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>10</v>
@@ -2815,7 +2727,7 @@
         <v>10584340</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>13</v>
@@ -2830,7 +2742,7 @@
         <v>16.2</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>1</v>
@@ -2839,22 +2751,22 @@
         <v>6.7</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>46538</v>
@@ -2863,19 +2775,19 @@
         <v>3000000</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X14" s="5"/>
       <c r="Y14" s="2" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="Z14" s="9" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>14</v>
@@ -2884,7 +2796,7 @@
         <v>54</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>10</v>
@@ -2893,7 +2805,7 @@
         <v>10584340</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>13</v>
@@ -2908,7 +2820,7 @@
         <v>15.5</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>1</v>
@@ -2917,22 +2829,22 @@
         <v>6.7</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>46503</v>
@@ -2941,19 +2853,19 @@
         <v>2217391.30434783</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X15" s="5"/>
       <c r="Y15" s="2" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="Z15" s="9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
@@ -2962,7 +2874,7 @@
         <v>50</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>10</v>
@@ -2971,7 +2883,7 @@
         <v>10584340</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H16" s="8" t="n">
         <v>13</v>
@@ -2986,7 +2898,7 @@
         <v>12.7</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1</v>
@@ -2995,22 +2907,22 @@
         <v>6.7</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>46387</v>
@@ -3019,21 +2931,21 @@
         <v>1140000</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X16" s="5" t="n">
         <v>850000</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="Z16" s="9" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>16</v>
@@ -3042,7 +2954,7 @@
         <v>49</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>16.7</v>
@@ -3051,7 +2963,7 @@
         <v>10584340</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>21.7</v>
@@ -3060,7 +2972,7 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>1</v>
@@ -3069,39 +2981,39 @@
         <v>11.1</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="5"/>
       <c r="W17" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="X17" s="5"/>
       <c r="Y17" s="2" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="Z17" s="9" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
@@ -3110,7 +3022,7 @@
         <v>48</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>10</v>
@@ -3119,7 +3031,7 @@
         <v>10584340</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>13</v>
@@ -3134,7 +3046,7 @@
         <v>11.9</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>1</v>
@@ -3143,22 +3055,22 @@
         <v>6.7</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>46357</v>
@@ -3167,21 +3079,21 @@
         <v>1000000</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X18" s="5" t="n">
         <v>1000000</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="Z18" s="9" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>18</v>
@@ -3190,7 +3102,7 @@
         <v>48</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>10</v>
@@ -3199,7 +3111,7 @@
         <v>10584340</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>13</v>
@@ -3214,7 +3126,7 @@
         <v>11.9</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>1</v>
@@ -3223,22 +3135,22 @@
         <v>6.7</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U19" s="4" t="n">
         <v>46438</v>
@@ -3247,21 +3159,21 @@
         <v>1000000</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X19" s="5" t="n">
         <v>350000</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="Z19" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
@@ -3270,7 +3182,7 @@
         <v>47</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>10</v>
@@ -3279,7 +3191,7 @@
         <v>127227</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>0.3</v>
@@ -3294,7 +3206,7 @@
         <v>11.9</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>1</v>
@@ -3303,22 +3215,22 @@
         <v>6.7</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>46497</v>
@@ -3327,19 +3239,19 @@
         <v>1000000</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X20" s="5"/>
       <c r="Y20" s="2" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="Z20" s="9" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>20</v>
@@ -3348,7 +3260,7 @@
         <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>10</v>
@@ -3357,7 +3269,7 @@
         <v>10584340</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>13</v>
@@ -3372,7 +3284,7 @@
         <v>10.6</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>1</v>
@@ -3381,22 +3293,22 @@
         <v>6.7</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>46464</v>
@@ -3405,19 +3317,19 @@
         <v>750000</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X21" s="5"/>
       <c r="Y21" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="Z21" s="9" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
@@ -3426,7 +3338,7 @@
         <v>44</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>10</v>
@@ -3435,7 +3347,7 @@
         <v>10584340</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>13</v>
@@ -3450,7 +3362,7 @@
         <v>9.6</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>1</v>
@@ -3459,22 +3371,22 @@
         <v>6.7</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U22" s="4" t="n">
         <v>46405</v>
@@ -3483,19 +3395,19 @@
         <v>700000</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X22" s="5"/>
       <c r="Y22" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="Z22" s="9" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>22</v>
@@ -3504,7 +3416,7 @@
         <v>44</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>10</v>
@@ -3513,7 +3425,7 @@
         <v>10584340</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>13</v>
@@ -3528,7 +3440,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>1</v>
@@ -3537,22 +3449,22 @@
         <v>6.7</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U23" s="4" t="n">
         <v>46468</v>
@@ -3561,21 +3473,21 @@
         <v>725000</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X23" s="5" t="n">
         <v>500000</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="Z23" s="9" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
@@ -3584,7 +3496,7 @@
         <v>43</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>10</v>
@@ -3593,7 +3505,7 @@
         <v>10584340</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>13</v>
@@ -3608,7 +3520,7 @@
         <v>9.4</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>1</v>
@@ -3617,22 +3529,22 @@
         <v>6.7</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U24" s="4" t="n">
         <v>46386</v>
@@ -3641,21 +3553,21 @@
         <v>685000</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X24" s="5" t="n">
         <v>150000</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="Z24" s="9" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>24</v>
@@ -3664,7 +3576,7 @@
         <v>42</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>10</v>
@@ -3673,7 +3585,7 @@
         <v>10584340</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>13</v>
@@ -3688,7 +3600,7 @@
         <v>9.2</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>1</v>
@@ -3697,22 +3609,22 @@
         <v>6.7</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U25" s="4" t="n">
         <v>46466</v>
@@ -3721,19 +3633,19 @@
         <v>650000</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X25" s="5"/>
       <c r="Y25" s="2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="Z25" s="9" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>25</v>
@@ -3742,7 +3654,7 @@
         <v>39</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>10</v>
@@ -3751,7 +3663,7 @@
         <v>10584340</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>13</v>
@@ -3766,7 +3678,7 @@
         <v>6.9</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>1</v>
@@ -3775,22 +3687,22 @@
         <v>6.7</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U26" s="4" t="n">
         <v>46462</v>
@@ -3799,21 +3711,21 @@
         <v>500000</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X26" s="5" t="n">
         <v>300000</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="Z26" s="9" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>26</v>
@@ -3822,7 +3734,7 @@
         <v>39</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>10</v>
@@ -3831,7 +3743,7 @@
         <v>10584340</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>13</v>
@@ -3846,7 +3758,7 @@
         <v>6.9</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>1</v>
@@ -3855,22 +3767,22 @@
         <v>6.7</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U27" s="4" t="n">
         <v>46532</v>
@@ -3879,21 +3791,21 @@
         <v>500000</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X27" s="5" t="n">
         <v>250000</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="Z27" s="9" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>27</v>
@@ -3902,7 +3814,7 @@
         <v>35</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>10</v>
@@ -3911,7 +3823,7 @@
         <v>10584340</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>13</v>
@@ -3926,7 +3838,7 @@
         <v>3.9</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>1</v>
@@ -3935,22 +3847,22 @@
         <v>6.7</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U28" s="4" t="n">
         <v>46508</v>
@@ -3959,14 +3871,14 @@
         <v>300000</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X28" s="5"/>
       <c r="Y28" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="Z28" s="9" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -4040,87 +3952,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -4129,7 +4041,7 @@
         <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E2" s="12" t="n">
         <v>20</v>
@@ -4138,7 +4050,7 @@
         <v>10584340</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H2" s="12" t="n">
         <v>13</v>
@@ -4153,7 +4065,7 @@
         <v>17.3</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -4162,22 +4074,22 @@
         <v>6.7</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>46429</v>
@@ -4186,21 +4098,21 @@
         <v>5000000</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X2" s="5" t="n">
         <v>50000</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="Z2" s="9" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -4209,7 +4121,7 @@
         <v>61</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>20</v>
@@ -4218,7 +4130,7 @@
         <v>127227</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="H3" s="12" t="n">
         <v>0.3</v>
@@ -4233,7 +4145,7 @@
         <v>15.3</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>1</v>
@@ -4242,22 +4154,22 @@
         <v>6.7</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U3" s="4" t="n">
         <v>46510</v>
@@ -4266,19 +4178,19 @@
         <v>2141025.64102564</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X3" s="5"/>
       <c r="Y3" s="2" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -4287,7 +4199,7 @@
         <v>61</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>10</v>
@@ -4296,7 +4208,7 @@
         <v>2322823</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H4" s="12" t="n">
         <v>4.7</v>
@@ -4311,7 +4223,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>1</v>
@@ -4320,22 +4232,22 @@
         <v>6.7</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>46661</v>
@@ -4344,21 +4256,21 @@
         <v>100000000</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>1000000</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4</v>
@@ -4367,7 +4279,7 @@
         <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>10</v>
@@ -4376,7 +4288,7 @@
         <v>10584340</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H5" s="12" t="n">
         <v>13</v>
@@ -4391,7 +4303,7 @@
         <v>17.8</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>1</v>
@@ -4400,22 +4312,22 @@
         <v>6.7</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U5" s="4" t="n">
         <v>46331</v>
@@ -4424,21 +4336,21 @@
         <v>6000000</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>1750000</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
@@ -4447,7 +4359,7 @@
         <v>60</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>10</v>
@@ -4456,7 +4368,7 @@
         <v>10584340</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>13</v>
@@ -4471,7 +4383,7 @@
         <v>17.7</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>1</v>
@@ -4480,22 +4392,22 @@
         <v>6.7</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>46357</v>
@@ -4504,21 +4416,21 @@
         <v>5750000</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X6" s="5" t="n">
         <v>3000000</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="Z6" s="9" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>6</v>
@@ -4527,7 +4439,7 @@
         <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>20</v>
@@ -4536,7 +4448,7 @@
         <v>10584340</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>13</v>
@@ -4551,7 +4463,7 @@
         <v>12.4</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
@@ -4560,22 +4472,22 @@
         <v>6.7</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>46507</v>
@@ -4584,19 +4496,19 @@
         <v>1002916.66666667</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X7" s="5"/>
       <c r="Y7" s="2" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="Z7" s="9" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
@@ -4605,7 +4517,7 @@
         <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>10</v>
@@ -4614,7 +4526,7 @@
         <v>10584340</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>13</v>
@@ -4629,7 +4541,7 @@
         <v>17.1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>1</v>
@@ -4638,22 +4550,22 @@
         <v>6.7</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>46412</v>
@@ -4662,21 +4574,21 @@
         <v>4900000</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>790000</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="Z8" s="9" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>8</v>
@@ -4685,7 +4597,7 @@
         <v>58</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>10</v>
@@ -4694,7 +4606,7 @@
         <v>10584340</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>13</v>
@@ -4709,7 +4621,7 @@
         <v>16.8</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>1</v>
@@ -4718,22 +4630,22 @@
         <v>6.7</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U9" s="4" t="n">
         <v>46469</v>
@@ -4742,19 +4654,19 @@
         <v>3625000</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X9" s="5"/>
       <c r="Y9" s="2" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="Z9" s="9" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
@@ -4763,14 +4675,14 @@
         <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="11"/>
@@ -4779,7 +4691,7 @@
         <v>28.9</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>1</v>
@@ -4788,22 +4700,22 @@
         <v>11.1</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>46469</v>
@@ -4812,21 +4724,21 @@
         <v>5000000</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X10" s="5" t="n">
         <v>5000000</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="Z10" s="9" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>10</v>
@@ -4835,7 +4747,7 @@
         <v>57</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>10</v>
@@ -4844,7 +4756,7 @@
         <v>2322823</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>4.7</v>
@@ -4859,7 +4771,7 @@
         <v>18</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>1</v>
@@ -4868,22 +4780,22 @@
         <v>6.7</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U11" s="4" t="n">
         <v>46498</v>
@@ -4892,21 +4804,21 @@
         <v>6750000</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X11" s="5" t="n">
         <v>6750000</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="Z11" s="9" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>11</v>
@@ -4915,7 +4827,7 @@
         <v>56</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>10</v>
@@ -4924,7 +4836,7 @@
         <v>2322823</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>4.7</v>
@@ -4939,7 +4851,7 @@
         <v>17.3</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>1</v>
@@ -4948,22 +4860,22 @@
         <v>6.7</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>46441</v>
@@ -4972,21 +4884,21 @@
         <v>5000000</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X12" s="5" t="n">
         <v>5000000</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="Z12" s="9" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>12</v>
@@ -4995,14 +4907,14 @@
         <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>33.3</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="11"/>
@@ -5011,7 +4923,7 @@
         <v>11.6</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>1</v>
@@ -5020,22 +4932,22 @@
         <v>11.1</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>46483</v>
@@ -5044,19 +4956,19 @@
         <v>500000</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X13" s="5"/>
       <c r="Y13" s="2" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="Z13" s="9" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
@@ -5065,7 +4977,7 @@
         <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>20</v>
@@ -5074,7 +4986,7 @@
         <v>1402172</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>2.7</v>
@@ -5089,7 +5001,7 @@
         <v>13</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>1</v>
@@ -5098,22 +5010,22 @@
         <v>6.7</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>46494</v>
@@ -5122,21 +5034,21 @@
         <v>1200000</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X14" s="5" t="n">
         <v>650000</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="Z14" s="9" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>14</v>
@@ -5145,7 +5057,7 @@
         <v>56</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>10</v>
@@ -5154,7 +5066,7 @@
         <v>10584340</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>13</v>
@@ -5169,7 +5081,7 @@
         <v>15.9</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>1</v>
@@ -5178,22 +5090,22 @@
         <v>6.7</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>46539</v>
@@ -5202,19 +5114,19 @@
         <v>2750000</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X15" s="5"/>
       <c r="Y15" s="2" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="Z15" s="9" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
@@ -5223,7 +5135,7 @@
         <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>20</v>
@@ -5232,7 +5144,7 @@
         <v>2322823</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>4.7</v>
@@ -5247,7 +5159,7 @@
         <v>9.6</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1</v>
@@ -5256,22 +5168,22 @@
         <v>6.7</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>46498</v>
@@ -5280,21 +5192,21 @@
         <v>700000</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X16" s="5" t="n">
         <v>700000</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="Z16" s="9" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>16</v>
@@ -5303,7 +5215,7 @@
         <v>51</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>10</v>
@@ -5312,7 +5224,7 @@
         <v>10584340</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>13</v>
@@ -5327,7 +5239,7 @@
         <v>13.4</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>1</v>
@@ -5336,22 +5248,22 @@
         <v>6.7</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U17" s="4" t="n">
         <v>46444</v>
@@ -5360,21 +5272,21 @@
         <v>1400000</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X17" s="5" t="n">
         <v>500000</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="Z17" s="9" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
@@ -5383,7 +5295,7 @@
         <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>10</v>
@@ -5392,7 +5304,7 @@
         <v>10584340</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>13</v>
@@ -5407,7 +5319,7 @@
         <v>13.5</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>1</v>
@@ -5416,22 +5328,22 @@
         <v>6.7</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>46454</v>
@@ -5440,19 +5352,19 @@
         <v>1423076.92307692</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X18" s="5"/>
       <c r="Y18" s="2" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="Z18" s="9" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>18</v>
@@ -5461,7 +5373,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>10</v>
@@ -5470,7 +5382,7 @@
         <v>1402172</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>2.7</v>
@@ -5485,7 +5397,7 @@
         <v>15.7</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>1</v>
@@ -5494,22 +5406,22 @@
         <v>6.7</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U19" s="4" t="n">
         <v>46461</v>
@@ -5518,19 +5430,19 @@
         <v>2500000</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="X19" s="5"/>
       <c r="Y19" s="2" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="Z19" s="9" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
@@ -5539,7 +5451,7 @@
         <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>16.7</v>
@@ -5548,7 +5460,7 @@
         <v>10584340</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>21.7</v>
@@ -5557,7 +5469,7 @@
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
       <c r="L20" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>1</v>
@@ -5566,41 +5478,41 @@
         <v>11.1</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>46783</v>
       </c>
       <c r="V20" s="5"/>
       <c r="W20" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="X20" s="5"/>
       <c r="Y20" s="2" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="Z20" s="9" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>20</v>
@@ -5609,7 +5521,7 @@
         <v>48</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>10</v>
@@ -5618,7 +5530,7 @@
         <v>10584340</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>13</v>
@@ -5633,7 +5545,7 @@
         <v>11.9</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>1</v>
@@ -5642,22 +5554,22 @@
         <v>6.7</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>46331</v>
@@ -5666,21 +5578,21 @@
         <v>1000000</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X21" s="5" t="n">
         <v>750000</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="Z21" s="9" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
@@ -5689,7 +5601,7 @@
         <v>46</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>10</v>
@@ -5698,7 +5610,7 @@
         <v>10584340</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>13</v>
@@ -5713,7 +5625,7 @@
         <v>11.3</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>1</v>
@@ -5722,22 +5634,22 @@
         <v>6.7</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U22" s="4" t="n">
         <v>46455</v>
@@ -5746,21 +5658,21 @@
         <v>900000</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X22" s="5" t="n">
         <v>450000</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="Z22" s="9" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>22</v>
@@ -5769,7 +5681,7 @@
         <v>41</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>10</v>
@@ -5778,7 +5690,7 @@
         <v>10584340</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>13</v>
@@ -5793,7 +5705,7 @@
         <v>8.4</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>1</v>
@@ -5802,22 +5714,22 @@
         <v>6.7</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U23" s="4" t="n">
         <v>47052</v>
@@ -5826,21 +5738,21 @@
         <v>550000</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X23" s="5" t="n">
         <v>50000</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="Z23" s="9" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
@@ -5849,7 +5761,7 @@
         <v>37</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>10</v>
@@ -5858,7 +5770,7 @@
         <v>10584340</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>13</v>
@@ -5873,7 +5785,7 @@
         <v>5.3</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>1</v>
@@ -5882,22 +5794,22 @@
         <v>6.7</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U24" s="4" t="n">
         <v>46510</v>
@@ -5906,21 +5818,21 @@
         <v>450000</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X24" s="5" t="n">
         <v>450000</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="Z24" s="9" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>24</v>
@@ -5929,7 +5841,7 @@
         <v>29</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>16.7</v>
@@ -5938,7 +5850,7 @@
         <v>618846</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>1.7</v>
@@ -5947,7 +5859,7 @@
       <c r="J25" s="12"/>
       <c r="K25" s="12"/>
       <c r="L25" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>1</v>
@@ -5956,34 +5868,34 @@
         <v>11.1</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="5"/>
       <c r="W25" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="X25" s="5"/>
       <c r="Y25" s="2" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="Z25" s="9" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -6054,87 +5966,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -6143,7 +6055,7 @@
         <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E2" s="15" t="n">
         <v>20</v>
@@ -6152,7 +6064,7 @@
         <v>10584340</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H2" s="15" t="n">
         <v>13</v>
@@ -6167,7 +6079,7 @@
         <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -6176,22 +6088,22 @@
         <v>6.7</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>46346</v>
@@ -6200,21 +6112,21 @@
         <v>15000000</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X2" s="5" t="n">
         <v>500000</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="Z2" s="9" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -6223,7 +6135,7 @@
         <v>67</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E3" s="15" t="n">
         <v>20</v>
@@ -6232,7 +6144,7 @@
         <v>127227</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="H3" s="15" t="n">
         <v>0.3</v>
@@ -6247,7 +6159,7 @@
         <v>19.9</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>1</v>
@@ -6256,22 +6168,22 @@
         <v>6.7</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U3" s="4" t="n">
         <v>46464</v>
@@ -6280,21 +6192,21 @@
         <v>48596938</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X3" s="5" t="n">
         <v>3285203</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -6303,7 +6215,7 @@
         <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E4" s="15" t="n">
         <v>10</v>
@@ -6312,7 +6224,7 @@
         <v>10584340</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H4" s="15" t="n">
         <v>13</v>
@@ -6327,7 +6239,7 @@
         <v>19.5</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>1</v>
@@ -6336,22 +6248,22 @@
         <v>6.7</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>46398</v>
@@ -6360,21 +6272,21 @@
         <v>22000000</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X4" s="5" t="n">
         <v>200000</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -6383,7 +6295,7 @@
         <v>77</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E5" s="15" t="n">
         <v>20</v>
@@ -6392,7 +6304,7 @@
         <v>618846</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>10</v>
@@ -6407,7 +6319,7 @@
         <v>20</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>1</v>
@@ -6416,43 +6328,43 @@
         <v>6.7</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="5" t="n">
         <v>275000000</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>260000</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
@@ -6461,7 +6373,7 @@
         <v>61</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E6" s="15" t="n">
         <v>33.3</v>
@@ -6470,7 +6382,7 @@
         <v>618846</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>16.7</v>
@@ -6479,7 +6391,7 @@
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
       <c r="L6" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>1</v>
@@ -6488,39 +6400,39 @@
         <v>11.1</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="5"/>
       <c r="W6" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="X6" s="5"/>
       <c r="Y6" s="2" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="Z6" s="9" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>3</v>
@@ -6529,7 +6441,7 @@
         <v>37</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E7" s="15" t="n">
         <v>20</v>
@@ -6538,7 +6450,7 @@
         <v>618846</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>10</v>
@@ -6553,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
@@ -6562,22 +6474,22 @@
         <v>6.7</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>46486</v>
@@ -6586,16 +6498,16 @@
         <v>400000</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>50000</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="Z7" s="9" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/outs/todo/09_top_results_with_rationale.xlsx
+++ b/outs/todo/09_top_results_with_rationale.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="403">
   <si>
-    <t xml:space="preserve">Our tool sorted grant opportunities into three tiers, instead of a singular list. These tiers are differentiated by the level of authority needed from a grant coordinator's perspective. Tier 1 grants can be directly acted upon by the grant writer using the tool. Tier 2 opportunities would need approval by a supervisor. Tier 3 grants, due to high matching costs or other factors, need oversight from upper legislature. The 3 tiers allow a user to make desicions about opportunities based on their capabilities and their priorities. Furthermore, within the tiers, the grants are sorted based on an "impact score" which is calculated with multiple metrics, including plan fit with the agency, people reached, population reached, help per person, and award size. While the weights for these metrics were equal, a user of our tool can adjust these weights according to their priorities. Also, there are a few opportunities chosen for the DMVA on this list, to showcase the generalizability of our model.</t>
+    <t xml:space="preserve">Our tool sorted grant opportunities into three tiers, instead of a singular list. These tiers are differentiated by the level of authority needed from a grant coordinator's perspective. Tier 1 grants can be directly acted upon by the grant writer using the tool. Tier 2 opportunities would need approval by a supervisor. Tier 3 grants, due to high matching costs or other factors, need approval from the secretary or the legislature. The 3 tiers allow a user to make decisions about opportunities based on their capabilities and their priorities. Furthermore, within the tiers, the grants are sorted based on an "impact score" which is calculated with multiple metrics, including plan fit with the agency's strategic plan, people reached, help per person, award size, and program priorities. While the weights for these metrics were equal, a user of our tool can adjust these weights according to their priorities. Also, there are a few opportunities chosen for the DMVA on this list, to showcase the generalizability of our model.</t>
   </si>
   <si>
     <t xml:space="preserve">How these results were ranked:</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">HHS-ACF</t>
   </si>
   <si>
-    <t xml:space="preserve">Top ranked in Tier 3 for strong plan fit and a large award (up to $15M), funding statewide early care, education data and technology infrastructure, but its 30% match and required state designation need the secretary.</t>
+    <t xml:space="preserve">Top ranked in Tier 3 for strong plan fit and a large award (up to $15M), funding statewide early care and education data and technology infrastructure, but its 30% match and required state designation need the secretary.</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/8d272419-96d1-4898-9706-0d86a1e63c03</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">VA-CSHF</t>
   </si>
   <si>
-    <t xml:space="preserve">Top ranked for DMVA strong plan fit, the highest help per veteran (about $444), and funding construction and modernization of State Veterans Homes, but needs a 35% state match and an appropriation.</t>
+    <t xml:space="preserve">Top ranked for DMVA for strong plan fit, the highest help per veteran (about $444), and funding construction and modernization of State Veterans Homes, but needs a 35% state match and an appropriation.</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/59462b36-6d05-4832-a628-427f72260f3d</t>
